--- a/Save/Save/Table2_Compare_Original.xlsx
+++ b/Save/Save/Table2_Compare_Original.xlsx
@@ -484,42 +484,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.520</t>
+          <t>0.524</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.524</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>0.798</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.716</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.610</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>0.548</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.386</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>0.822</t>
         </is>
       </c>
     </row>
@@ -536,32 +536,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.482</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.802</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>0.729</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.802</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.729</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>0.611</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>0.486</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -583,32 +583,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.503</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.797</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>0.709</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.797</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.709</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>0.568</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>0.520</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.401</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -630,32 +630,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.521</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.806</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>0.723</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.806</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.723</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>0.585</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>0.539</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.380</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -677,32 +677,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.811</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>0.731</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.811</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.731</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,32 +724,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.530</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.803</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>0.726</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.803</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.726</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.621</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.554</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -771,32 +771,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.519</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.806</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>0.721</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.806</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.721</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>0.536</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.386</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -818,32 +818,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.483</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.772</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>0.643</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.643</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>0.492</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>0.486</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>0.645</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -865,32 +865,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.456</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.789</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>0.721</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.789</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.721</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.449</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.386</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -912,32 +912,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.494</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.786</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>0.703</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.786</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.703</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>0.563</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1020,32 +1020,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.572</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.869</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>0.757</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.721</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.757</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.640</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1067,27 +1067,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.541</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.895</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>0.761</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.718</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.761</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.760</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>0.631</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1114,27 +1114,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.598</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.860</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>0.761</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.729</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.761</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.722</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1161,27 +1161,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.593</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.876</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>0.769</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.734</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.769</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>0.743</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>0.660</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1208,27 +1208,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.593</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.879</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>0.771</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.736</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.771</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>0.748</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>0.662</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1255,27 +1255,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.573</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.888</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>0.769</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.731</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.769</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.756</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>0.652</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1302,27 +1302,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.593</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.881</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>0.772</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.770</t>
+          <t>0.752</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>0.663</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1349,27 +1349,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.614</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.798</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>0.729</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.706</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.729</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>0.649</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.631</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1396,27 +1396,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.508</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.913</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>0.760</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.710</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>0.780</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1443,27 +1443,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.461</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>0.737</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.682</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>0.745</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.569</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">

--- a/Save/Save/Table2_Compare_Original.xlsx
+++ b/Save/Save/Table2_Compare_Original.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiClass" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_SMOTE" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1480,4 +1481,535 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>F1-score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Brier Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ROC-AUC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.722</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.682</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.762</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.732</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.635</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.178</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.801</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.731</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.584</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.879</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.767</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.745</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.655</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.819</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.726</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.598</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.854</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.757</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.714</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.651</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.167</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.813</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.732</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.592</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.766</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.738</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.657</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.159</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.743</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.621</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.865</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.773</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.737</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.674</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.155</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.834</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.594</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.848</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.752</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.705</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.645</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.164</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.815</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HistGradientBoosting</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.723</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.576</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.870</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.759</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.729</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.644</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.162</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.818</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MLPClassifier</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.638</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.774</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.722</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.631</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.252</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.763</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.736</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.806</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.753</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.676</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.672</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.804</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KNeighbors</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.691</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.734</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.648</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.680</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.558</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.221</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.754</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Save/Save/Table2_Compare_Original.xlsx
+++ b/Save/Save/Table2_Compare_Original.xlsx
@@ -7,9 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiClass" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_SMOTE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiClass_macro" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiClass_weighted" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_SMOTE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Calibrated" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1016,42 +1019,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.524</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>0.716</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>0.798</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.716</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.610</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.640</t>
+          <t>0.548</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.386</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>0.822</t>
         </is>
       </c>
     </row>
@@ -1063,42 +1066,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>0.482</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>0.729</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.895</t>
+          <t>0.802</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>0.729</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.611</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>0.486</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.374</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>0.835</t>
         </is>
       </c>
     </row>
@@ -1110,42 +1113,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>0.503</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.598</t>
+          <t>0.709</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.860</t>
+          <t>0.797</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>0.709</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.568</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>0.520</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.401</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>0.818</t>
         </is>
       </c>
     </row>
@@ -1157,42 +1160,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>0.521</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>0.723</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>0.806</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>0.723</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>0.585</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.660</t>
+          <t>0.539</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.160</t>
+          <t>0.380</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>0.831</t>
         </is>
       </c>
     </row>
@@ -1204,42 +1207,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>0.525</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>0.731</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>0.811</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>0.731</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.748</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>0.545</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>0.835</t>
         </is>
       </c>
     </row>
@@ -1251,42 +1254,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>0.530</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>0.726</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>0.803</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>0.726</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>0.621</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>0.554</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.376</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>0.832</t>
         </is>
       </c>
     </row>
@@ -1298,42 +1301,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.519</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>0.721</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>0.806</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.721</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>0.583</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>0.536</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.386</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>0.827</t>
         </is>
       </c>
     </row>
@@ -1345,42 +1348,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.483</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>0.643</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>0.643</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>0.492</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>0.486</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>0.645</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.721</t>
         </is>
       </c>
     </row>
@@ -1392,42 +1395,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.710</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.508</t>
+          <t>0.721</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.789</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.760</t>
+          <t>0.721</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.780</t>
+          <t>0.457</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>0.449</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.386</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>0.828</t>
         </is>
       </c>
     </row>
@@ -1439,42 +1442,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.494</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>0.703</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.703</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>0.563</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.439</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>0.735</t>
         </is>
       </c>
     </row>
@@ -1547,42 +1550,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.721</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.572</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>0.869</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.640</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>0.802</t>
         </is>
       </c>
     </row>
@@ -1594,42 +1597,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>0.718</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>0.541</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>0.895</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.631</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>0.817</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1644,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>0.729</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1651,32 +1654,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.854</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.722</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>0.811</t>
         </is>
       </c>
     </row>
@@ -1688,42 +1691,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>0.734</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>0.876</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>0.743</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.657</t>
+          <t>0.660</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.160</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.819</t>
         </is>
       </c>
     </row>
@@ -1735,42 +1738,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>0.736</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>0.771</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.748</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>0.662</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>0.832</t>
         </is>
       </c>
     </row>
@@ -1782,42 +1785,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.731</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.573</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>0.888</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.756</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>0.652</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>0.814</t>
         </is>
       </c>
     </row>
@@ -1829,42 +1832,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.870</t>
+          <t>0.881</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>0.752</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>0.663</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0.822</t>
         </is>
       </c>
     </row>
@@ -1881,37 +1884,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.798</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.729</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>0.649</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>0.631</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.634</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>0.757</t>
         </is>
       </c>
     </row>
@@ -1923,42 +1926,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>0.710</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.508</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>0.913</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>0.760</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>0.780</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>0.807</t>
         </is>
       </c>
     </row>
@@ -1970,6 +1973,537 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>0.682</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.461</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.737</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.745</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.569</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.194</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.754</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>F1-score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Brier Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ROC-AUC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.722</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.682</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.762</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.732</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.635</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.178</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.801</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.731</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.584</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.879</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.767</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.745</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.655</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.819</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.726</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.598</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.854</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.757</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.714</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.651</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.167</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.813</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LightGBM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.732</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.592</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.766</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.738</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.657</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.159</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.743</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.621</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.865</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.773</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.737</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.674</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.155</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.834</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.594</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.848</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.752</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.705</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.645</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.164</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.815</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HistGradientBoosting</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.723</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.576</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.870</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.759</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.729</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.644</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.162</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.818</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MLPClassifier</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.638</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.774</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.722</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.631</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.252</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.763</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.736</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.806</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.753</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.676</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.672</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.804</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KNeighbors</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>0.691</t>
         </is>
       </c>
@@ -2006,6 +2540,352 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0.754</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>F1-score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Brier Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ROC-AUC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Logistic Regression + Cal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.721</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.584</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.857</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.754</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.713</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.642</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.169</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.801</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LightGBM + Cal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.736</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.567</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.777</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.783</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.157</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.826</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XGBoost + Cal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.734</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.896</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.773</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.770</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.656</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.158</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.828</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CatBoost + Cal</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.734</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.580</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.888</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.772</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.759</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.156</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.831</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Multiclass Note (KR): 멀티클래스에서 Balanced Accuracy는 정의상 macro-averaged recall과 동일함(=macro Sensitivity).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>중복을 피하기 위해 본 표의 멀티클래스 Sensitivity는 weighted-averaged recall로도 제시함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Specificity는 One-vs-Rest TNR을 클래스별로 계산한 뒤 macro 평균으로 산출함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>micro-averaged recall은 단일 레이블 분류에서 Accuracy와 동일하므로 해석 시 중복 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Multiclass Note (EN): In multiclass classification, Balanced Accuracy is identical to macro-averaged recall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>To avoid redundancy, we also report Sensitivity as weighted-averaged recall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Specificity is computed as one-vs-rest TNR and averaged across classes (macro).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Micro-averaged recall equals accuracy in single-label settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Binary (SMOTE) Note: We applied SMOTE (k=5, random_state=42) to the TRAIN set only; the TEST set remained unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Calibration Note: Probability calibration (isotonic, 5-fold CV) was applied on the TRAIN set only; we report pre/post Brier and AUC.</t>
         </is>
       </c>
     </row>

--- a/Save/Save/Table2_Compare_Original.xlsx
+++ b/Save/Save/Table2_Compare_Original.xlsx
@@ -9,10 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiClass_macro" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiClass_weighted" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_SMOTE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Calibrated" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiClass_Stack" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_SMOTE" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Calibrated" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Stack" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Stack_SMOTE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1492,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1545,470 +1548,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Stacking (meta=LR)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.510</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>0.805</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.612</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.640</t>
+          <t>0.529</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.802</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0.718</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.541</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.895</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.761</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.757</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.631</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.164</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.817</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.729</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.598</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.860</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.761</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.722</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.654</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.168</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.811</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.734</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.593</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.876</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.769</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.743</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.660</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.160</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.819</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CatBoost</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.736</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.593</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.879</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.771</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.748</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.662</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.156</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.832</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.731</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.573</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.888</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.769</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.756</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.652</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.162</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.814</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HistGradientBoosting</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.593</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.881</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.752</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.663</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.159</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.822</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MLPClassifier</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.706</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0.614</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.798</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.729</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.649</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.631</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.248</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.757</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SVC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0.710</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.508</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.913</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.780</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.166</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.807</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KNeighbors</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0.682</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.461</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.904</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.745</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.569</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.194</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.754</t>
+          <t>0.834</t>
         </is>
       </c>
     </row>
@@ -2081,42 +1661,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.721</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.572</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>0.869</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.640</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>0.802</t>
         </is>
       </c>
     </row>
@@ -2128,42 +1708,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>0.718</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>0.541</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>0.895</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.631</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>0.817</t>
         </is>
       </c>
     </row>
@@ -2175,7 +1755,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>0.729</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2185,32 +1765,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.854</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.722</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>0.811</t>
         </is>
       </c>
     </row>
@@ -2222,42 +1802,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>0.734</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>0.876</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>0.743</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.657</t>
+          <t>0.660</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.160</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.819</t>
         </is>
       </c>
     </row>
@@ -2269,42 +1849,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>0.736</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>0.771</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.748</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>0.662</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>0.832</t>
         </is>
       </c>
     </row>
@@ -2316,42 +1896,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.731</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.573</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>0.888</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.756</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>0.652</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>0.814</t>
         </is>
       </c>
     </row>
@@ -2363,42 +1943,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.870</t>
+          <t>0.881</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>0.752</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>0.663</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0.822</t>
         </is>
       </c>
     </row>
@@ -2415,37 +1995,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.798</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.729</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>0.649</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>0.631</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.634</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>0.757</t>
         </is>
       </c>
     </row>
@@ -2457,42 +2037,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>0.710</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.508</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>0.913</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>0.760</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>0.780</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>0.807</t>
         </is>
       </c>
     </row>
@@ -2504,37 +2084,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>0.461</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>0.904</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>0.745</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>0.569</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2554,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2607,42 +2187,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Logistic Regression + Cal</t>
+          <t>Logistic Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.722</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.762</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>0.732</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>0.635</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>0.658</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2654,141 +2234,423 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LightGBM + Cal</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>0.731</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>0.584</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>0.767</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.745</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.655</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>0.819</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XGBoost + Cal</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>0.726</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.598</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.896</t>
+          <t>0.854</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.770</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>0.651</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>0.813</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CatBoost + Cal</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>0.732</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.592</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.766</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.738</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.657</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.159</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.743</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.621</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.865</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.773</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.737</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.674</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.155</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.834</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.594</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.848</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.752</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.705</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.645</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.164</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.815</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HistGradientBoosting</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.723</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.576</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.870</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.759</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.729</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.644</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.162</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.818</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MLPClassifier</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.638</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.774</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.722</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.631</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.252</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.763</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.736</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.806</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.753</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.676</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.672</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.804</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KNeighbors</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.691</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>0.734</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.580</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.888</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.759</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.658</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.156</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.831</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.648</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.680</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.558</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.221</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.754</t>
         </is>
       </c>
     </row>
@@ -2803,40 +2665,505 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>F1-score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Brier Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ROC-AUC</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Multiclass Note (KR): 멀티클래스에서 Balanced Accuracy는 정의상 macro-averaged recall과 동일함(=macro Sensitivity).</t>
+          <t>Logistic Regression + Cal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.721</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.584</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.857</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.754</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.713</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.642</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.169</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.801</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>중복을 피하기 위해 본 표의 멀티클래스 Sensitivity는 weighted-averaged recall로도 제시함.</t>
+          <t>LightGBM + Cal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.736</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.567</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.777</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.783</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.157</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.826</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Specificity는 One-vs-Rest TNR을 클래스별로 계산한 뒤 macro 평균으로 산출함.</t>
+          <t>XGBoost + Cal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.734</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.896</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.773</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.770</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.656</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.158</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.828</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>CatBoost + Cal</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.734</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.580</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.888</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.772</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.759</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.156</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.831</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>F1-score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Brier Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ROC-AUC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Stacking (meta=LR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.734</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.593</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.876</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.769</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.743</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.660</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.158</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>F1-score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Brier Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ROC-AUC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Stacking + SMOTE (meta=LR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.739</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.622</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.856</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.767</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.724</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.669</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.159</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.827</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Multiclass Note (KR): 멀티클래스에서 Balanced Accuracy는 정의상 macro-averaged recall과 동일함(=macro Sensitivity).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>중복을 피하기 위해 본 표의 멀티클래스 Sensitivity는 weighted-averaged recall로도 제시함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Specificity는 One-vs-Rest TNR을 클래스별로 계산한 뒤 macro 평균으로 산출함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>micro-averaged recall은 단일 레이블 분류에서 Accuracy와 동일하므로 해석 시 중복 가능.</t>
         </is>
       </c>
@@ -2886,6 +3213,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>Calibration Note: Probability calibration (isotonic, 5-fold CV) was applied on the TRAIN set only; we report pre/post Brier and AUC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Stacking Note: Stacking uses LGBM/XGB/CatBoost/LR as base learners and Logistic Regression (lbfgs) as meta-learner with passthrough=True.</t>
         </is>
       </c>
     </row>

--- a/Save/Save/Table2_Compare_Original.xlsx
+++ b/Save/Save/Table2_Compare_Original.xlsx
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>0.799</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>0.815</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0.800</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.831</t>
+          <t>0.815</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>0.815</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>0.811</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>0.812</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.715</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>0.803</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>0.743</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>0.815</t>
         </is>
       </c>
     </row>
@@ -3143,28 +3143,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Multiclass Note (KR): 멀티클래스에서 Balanced Accuracy는 정의상 macro-averaged recall과 동일함(=macro Sensitivity).</t>
+          <t>Multiclass Note (KR): Balanced Accuracy는 정의상 macro-averaged recall과 동일.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>중복을 피하기 위해 본 표의 멀티클래스 Sensitivity는 weighted-averaged recall로도 제시함.</t>
+          <t>본 연구에서는 멀티클래스 표에서 Sensitivity 평균 방식과 AUC 평균 방식을 각각 macro/weighted로 일치시켜 보고함.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Specificity는 One-vs-Rest TNR을 클래스별로 계산한 뒤 macro 평균으로 산출함.</t>
+          <t>Specificity는 One-vs-Rest TNR을 클래스별로 계산한 뒤 macro 평균으로 산출.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>micro-averaged recall은 단일 레이블 분류에서 Accuracy와 동일하므로 해석 시 중복 가능.</t>
+          <t>micro-averaged recall은 단일 레이블 분류에서 Accuracy와 동일.</t>
         </is>
       </c>
     </row>
@@ -3174,21 +3174,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multiclass Note (EN): In multiclass classification, Balanced Accuracy is identical to macro-averaged recall.</t>
+          <t>Multiclass Note (EN): Balanced Accuracy is identical to macro-averaged recall.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>To avoid redundancy, we also report Sensitivity as weighted-averaged recall.</t>
+          <t>For multiclass tables, we align the averaging scheme of Sensitivity and ROC-AUC (macro or weighted).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Specificity is computed as one-vs-rest TNR and averaged across classes (macro).</t>
+          <t>Specificity is computed as one-vs-rest TNR (macro-averaged).</t>
         </is>
       </c>
     </row>
@@ -3205,14 +3205,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Binary (SMOTE) Note: We applied SMOTE (k=5, random_state=42) to the TRAIN set only; the TEST set remained unchanged.</t>
+          <t>Binary (SMOTE) Note: SMOTE (k=5) applied to TRAIN only; TEST unchanged.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Calibration Note: Probability calibration (isotonic, 5-fold CV) was applied on the TRAIN set only; we report pre/post Brier and AUC.</t>
+          <t>Calibration Note: Probability calibration (isotonic, 5-fold CV) applied on TRAIN only; pre/post Brier and AUC are reported.</t>
         </is>
       </c>
     </row>

--- a/Save/Save/Table2_Compare_Original.xlsx
+++ b/Save/Save/Table2_Compare_Original.xlsx
@@ -15,7 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Calibrated" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Stack" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Stack_SMOTE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_FrailOnly_SMOTENC_RF" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -958,6 +959,76 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Multiclass: Balanced Accuracy는 macro-averaged recall과 동일.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>멀티클래스 표에서 Sensitivity와 AUC의 averaging을 각 표에 맞춰(macro/weighted) 일치시켜 보고.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Specificity는 OvR TNR을 클래스별로 계산 후 macro 평균.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Binary: SMOTE(k=5)은 TRAIN에만 적용, TEST 분포 유지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Calibration: isotonic, 5-fold CV(Train) 후 성능 비교.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Stacking: LGBM/XGB/CatBoost/LR base + LR meta(passthrough=True).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Strict Binary: Prefrail 제외, SMOTENC → OHE/Scale → RF95% → CatBoost 튜닝.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3130,96 +3201,147 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>F1-score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Brier Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ROC-AUC</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Multiclass Note (KR): Balanced Accuracy는 정의상 macro-averaged recall과 동일.</t>
+          <t>CatBoost (SMOTENC+RF95)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.786</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.590</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.982</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.953</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.720</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.648</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.037</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.949</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>본 연구에서는 멀티클래스 표에서 Sensitivity 평균 방식과 AUC 평균 방식을 각각 macro/weighted로 일치시켜 보고함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Specificity는 One-vs-Rest TNR을 클래스별로 계산한 뒤 macro 평균으로 산출.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>micro-averaged recall은 단일 레이블 분류에서 Accuracy와 동일.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Multiclass Note (EN): Balanced Accuracy is identical to macro-averaged recall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>For multiclass tables, we align the averaging scheme of Sensitivity and ROC-AUC (macro or weighted).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Specificity is computed as one-vs-rest TNR (macro-averaged).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Micro-averaged recall equals accuracy in single-label settings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Binary (SMOTE) Note: SMOTE (k=5) applied to TRAIN only; TEST unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Calibration Note: Probability calibration (isotonic, 5-fold CV) applied on TRAIN only; pre/post Brier and AUC are reported.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Stacking Note: Stacking uses LGBM/XGB/CatBoost/LR as base learners and Logistic Regression (lbfgs) as meta-learner with passthrough=True.</t>
+          <t>CatBoost (SMOTENC only)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.801</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.620</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.982</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.955</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.729</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.670</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.034</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.950</t>
         </is>
       </c>
     </row>

--- a/Save/Save/Table2_Compare_Original.xlsx
+++ b/Save/Save/Table2_Compare_Original.xlsx
@@ -10,13 +10,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiClass_macro" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiClass_weighted" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiClass_Stack" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_SMOTE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Calibrated" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Stack" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Stack_SMOTE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_FrailOnly_SMOTENC_RF" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MultiClass_Stack_Strong" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_SMOTE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Calibrated" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Stack" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Stack_SMOTE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_Stack_Strong" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Binary_FrailOnly_SMOTENC_RF" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -965,26 +967,289 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>F1-score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Brier Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ROC-AUC</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Multiclass: Balanced Accuracy는 macro-averaged recall과 동일.</t>
+          <t>Stacking (meta=LGBM)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.727</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.580</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.873</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.762</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.735</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.649</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.167</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.804</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Balanced Accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>F1-score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Brier Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ROC-AUC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CatBoost (SMOTENC+RF95)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.786</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.590</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.982</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.953</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.720</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.648</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.037</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.949</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>CatBoost (SMOTENC only)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.801</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.620</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.982</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.955</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.729</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.670</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.034</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.950</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Multiclass: Balanced Accuracy는 macro-averaged recall과 동일.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>멀티클래스 표에서 Sensitivity와 AUC의 averaging을 각 표에 맞춰(macro/weighted) 일치시켜 보고.</t>
         </is>
       </c>
@@ -1019,6 +1284,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>Strong Stacking: 다양한 base + meta=LGBM, no passthrough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Strict Binary: Prefrail 제외, SMOTENC → OHE/Scale → RF95% → CatBoost 튜닝.</t>
         </is>
@@ -1674,7 +1946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1727,470 +1999,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Stacking (meta=LGBM)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.498</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>0.558</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.640</t>
+          <t>0.512</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>0.395</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>0.802</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0.718</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.541</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.895</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.761</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.757</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.631</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.164</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.817</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.729</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.598</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.860</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.761</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.722</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.654</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.168</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.811</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.734</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.593</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.876</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.769</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.743</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.660</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.160</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.819</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CatBoost</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.736</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.593</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.879</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.771</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.748</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.662</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.156</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.832</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.731</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.573</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.888</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.769</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.756</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0.652</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.162</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.814</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HistGradientBoosting</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.593</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.881</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.752</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.663</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.159</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.822</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MLPClassifier</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.706</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0.614</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.798</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.729</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.649</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.631</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.248</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.757</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SVC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0.710</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.508</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.913</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.760</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.780</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.166</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.807</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KNeighbors</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0.682</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.461</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.904</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.737</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.745</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.569</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.194</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.754</t>
         </is>
       </c>
     </row>
@@ -2263,42 +2112,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.721</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.572</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>0.869</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>0.727</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.640</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>0.802</t>
         </is>
       </c>
     </row>
@@ -2310,42 +2159,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>0.718</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>0.541</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>0.895</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>0.631</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>0.817</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2206,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>0.729</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2367,32 +2216,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.854</t>
+          <t>0.860</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>0.761</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>0.722</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.168</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.813</t>
+          <t>0.811</t>
         </is>
       </c>
     </row>
@@ -2404,42 +2253,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.732</t>
+          <t>0.734</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>0.876</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>0.743</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.657</t>
+          <t>0.660</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.160</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>0.819</t>
         </is>
       </c>
     </row>
@@ -2451,42 +2300,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>0.736</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>0.771</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>0.748</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>0.662</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>0.832</t>
         </is>
       </c>
     </row>
@@ -2498,42 +2347,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.731</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>0.573</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>0.888</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.756</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>0.652</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>0.814</t>
         </is>
       </c>
     </row>
@@ -2545,42 +2394,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.723</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.870</t>
+          <t>0.881</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>0.752</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>0.663</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0.822</t>
         </is>
       </c>
     </row>
@@ -2597,37 +2446,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>0.614</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.798</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.729</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>0.649</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>0.631</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.634</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>0.248</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>0.757</t>
         </is>
       </c>
     </row>
@@ -2639,42 +2488,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>0.710</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.508</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>0.913</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>0.760</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>0.780</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>0.615</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>0.807</t>
         </is>
       </c>
     </row>
@@ -2686,37 +2535,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>0.461</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>0.904</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.680</t>
+          <t>0.737</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>0.745</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>0.569</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2736,7 +2585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2789,42 +2638,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Logistic Regression + Cal</t>
+          <t>Logistic Regression</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.722</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>0.682</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.762</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>0.732</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>0.635</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>0.658</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2836,141 +2685,423 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LightGBM + Cal</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>0.731</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>0.584</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>0.767</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.745</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>0.655</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>0.819</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XGBoost + Cal</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>0.726</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>0.598</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.896</t>
+          <t>0.854</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>0.757</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.770</t>
+          <t>0.714</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>0.651</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>0.813</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CatBoost + Cal</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>0.732</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.592</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.872</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.766</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.738</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.657</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.159</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CatBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.743</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.621</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.865</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.773</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.737</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.674</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.155</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.834</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GradientBoosting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.721</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.594</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.848</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.752</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.705</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.645</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.164</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.815</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HistGradientBoosting</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.723</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.576</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.870</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.759</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.729</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.644</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.162</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.818</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MLPClassifier</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.638</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.774</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.722</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.631</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.252</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.763</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.736</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.806</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.753</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.676</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.672</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.804</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KNeighbors</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.691</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>0.734</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.580</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.888</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.759</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.658</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.156</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.831</t>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.648</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.680</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.558</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.634</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.221</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.754</t>
         </is>
       </c>
     </row>
@@ -2985,7 +3116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3038,47 +3169,188 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Stacking (meta=LR)</t>
+          <t>Logistic Regression + Cal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>0.721</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.584</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.857</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.754</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.713</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.642</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.169</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.801</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LightGBM + Cal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.736</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.567</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.777</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.783</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.157</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.826</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XGBoost + Cal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>0.734</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.593</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.876</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.769</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.743</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.660</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.896</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.773</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.770</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.656</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.158</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.824</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.828</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CatBoost + Cal</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.734</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.580</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.888</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.772</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.759</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.658</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.156</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.831</t>
         </is>
       </c>
     </row>
@@ -3146,47 +3418,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Stacking + SMOTE (meta=LR)</t>
+          <t>Stacking (meta=LR)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>0.734</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>0.593</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>0.876</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>0.743</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>0.660</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>0.824</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3254,94 +3526,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CatBoost (SMOTENC+RF95)</t>
+          <t>Stacking + SMOTE (meta=LR)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.739</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.590</t>
+          <t>0.622</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.982</t>
+          <t>0.856</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.953</t>
+          <t>0.767</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.720</t>
+          <t>0.724</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>0.669</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.159</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.949</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CatBoost (SMOTENC only)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0.801</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.620</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.982</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.955</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.729</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.670</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.034</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.950</t>
+          <t>0.827</t>
         </is>
       </c>
     </row>
